--- a/artfynd/A 37639-2024 artfynd.xlsx
+++ b/artfynd/A 37639-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6789749</v>
+        <v>6789776</v>
       </c>
       <c r="B2" t="n">
-        <v>73678</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6439</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Djupdalsberget, Jansfall, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481220.5039508186</v>
+        <v>481224</v>
       </c>
       <c r="R2" t="n">
-        <v>6679628.974161153</v>
+        <v>6679591</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,19 +752,9 @@
           <t>2013-06-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2013-06-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,6 +778,413 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6789777</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Djupdalsberget, Jansfall, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>481224</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6679591</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2013-06-01</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2013-06-01</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6789749</v>
+      </c>
+      <c r="B4" t="n">
+        <v>83290</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Djupdalsberget, Jansfall, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>481221</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6679629</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2013-06-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2013-06-01</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6789873</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Djupdalsberget, Jansfall, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>481111</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6679635</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2013-06-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2013-06-01</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Via Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6789779</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Djupdalsberget, Jansfall, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>481111</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6679635</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2013-06-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2013-06-01</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
